--- a/rtos-api-analysis/results/threadx-6.4.2_runtime_info_walltime.xlsx
+++ b/rtos-api-analysis/results/threadx-6.4.2_runtime_info_walltime.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.3022</v>
+        <v>1.2816</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>580.2619</v>
+        <v>2667.7377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -543,31 +543,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4585</v>
+        <v>0.4573</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>584752</t>
+          <t>369554</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>990</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.4943</v>
+        <v>12.5295</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0417</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.1391</v>
+        <v>2.8409</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51.5258</v>
+        <v>333.8066</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0326</v>
+        <v>0.0772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1854</v>
+        <v>5.0742</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0708</v>
+        <v>0.0931</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4548</v>
+        <v>2.4192</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4459</v>
+        <v>2.3276</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0193</v>
+        <v>0.0408</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>83.13079999999999</v>
+        <v>1010.2653</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1075,22 +1075,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>97609</t>
+          <t>94164</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.2973</v>
+        <v>7.497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2434</v>
+        <v>2.6018</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0324</v>
+        <v>0.0793</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.9756</v>
+        <v>20.8193</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0247</v>
+        <v>0.0148</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.8684</v>
+        <v>9.6494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0176</v>
+        <v>0.0152</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3142</v>
+        <v>0.4153</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0938</v>
+        <v>1.2905</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.8888</v>
+        <v>8.6265</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.9175</v>
+        <v>6.1331</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0363</v>
+        <v>0.0407</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.999</v>
+        <v>2.0593</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>66.68000000000001</v>
+        <v>2403.23</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1743,31 +1743,31 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.4422</v>
+        <v>0.4521</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>315270</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>840</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.9054</v>
+        <v>50.6283</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>287</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25099</t>
+          <t>25162</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>37.2041</v>
+        <v>67.87009999999999</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1843,17 +1843,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>42891</t>
+          <t>42867</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>737</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5608</v>
+        <v>0.376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.3052</v>
+        <v>1.8516</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.5172</v>
+        <v>2.6214</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0166</v>
+        <v>0.025</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>36000.4416</v>
+        <v>36001.5871</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.6797</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>450272</t>
+          <t>32449</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>18125875</t>
+          <t>1309793</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>399102</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>51170</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0557</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.3751</v>
+        <v>2.3788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.7347</v>
+        <v>1.5053</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>37.2554</v>
+        <v>113.0282</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0273</v>
+        <v>0.0756</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0511</v>
+        <v>0.1035</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.2715</v>
+        <v>4.8349</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.8492</v>
+        <v>3.7114</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0371</v>
+        <v>0.0805</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>6.2382</v>
+        <v>10.0044</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.7229</v>
+        <v>1.3617</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0501</v>
+        <v>0.1235</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.6178</v>
+        <v>3.0364</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6.8895</v>
+        <v>7.3723</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2755,17 +2755,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.3562</v>
+        <v>1.3413</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6.6941</v>
+        <v>9.486599999999999</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6.0782</v>
+        <v>9.6944</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.3185</v>
+        <v>1.3982</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4.068</v>
+        <v>4.0571</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3878</v>
+        <v>0.4155</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0353</v>
+        <v>0.0572</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4729</v>
+        <v>0.5468</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>150.854</v>
+        <v>829.5457</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.4847</v>
+        <v>0.487</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>166790</t>
+          <t>166794</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>50.7856</v>
+        <v>338.709</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3778</v>
+        <v>0.4887</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.7495</v>
+        <v>2.3903</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>18.1453</v>
+        <v>20.2725</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>20.2438</v>
+        <v>56.4259</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6.0689</v>
+        <v>7.8481</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3475,17 +3475,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>6.4189</v>
+        <v>10.1953</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>16.7621</v>
+        <v>12.4508</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2.9327</v>
+        <v>1.9092</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2.7318</v>
+        <v>3.9365</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>53.9765</v>
+        <v>59.6611</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3715,17 +3715,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>67629</t>
+          <t>68578</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>17.8643</v>
+        <v>20.389</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>7.8434</v>
+        <v>11.6969</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>18.4049</v>
+        <v>11.9538</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3.4425</v>
+        <v>4.2659</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0124</v>
+        <v>0.0254</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.8539</v>
+        <v>1.9694</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0014</v>
+        <v>0.4492</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4047,31 +4047,31 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>0.1631</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>166</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.0203</v>
+        <v>0.0388</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2.9806</v>
+        <v>1.5559</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>12.8426</v>
+        <v>24.9268</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4195,17 +4195,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.0759</v>
+        <v>0.0795</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0619</v>
+        <v>0.1189</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>19.3754</v>
+        <v>39.1411</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4339,17 +4339,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>328</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8129</v>
+        <v>0.6293</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>62.9529</v>
+        <v>76.16630000000001</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6.1878</v>
+        <v>10.3443</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>24.3844</v>
+        <v>26.1166</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3.9346</v>
+        <v>4.071</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>42.2746</v>
+        <v>161.9061</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.1205</v>
+        <v>0.1716</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>215.0931</v>
+        <v>1635.4804</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9.9747</v>
+        <v>7.8893</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>8.293799999999999</v>
+        <v>5.5849</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.3296</v>
+        <v>0.4213</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2.6907</v>
+        <v>2.2958</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2.4112</v>
+        <v>2.2476</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0141</v>
+        <v>0.042</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.547</v>
+        <v>0.5114</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
